--- a/RAE05X.xlsx
+++ b/RAE05X.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -67,7 +67,7 @@
     <t>20138341</t>
   </si>
   <si>
-    <t>KALULI YOGHURT 130ML</t>
+    <t>KALULI YOGHURT 90ML</t>
   </si>
   <si>
     <t>8</t>
@@ -109,6 +109,24 @@
     <t>14</t>
   </si>
   <si>
+    <t>20144210</t>
+  </si>
+  <si>
+    <t>KALULI GL BLCK CPN60</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20144209</t>
+  </si>
+  <si>
+    <t>KALULI GL ROSE COC60</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20139397</t>
   </si>
   <si>
@@ -181,16 +199,10 @@
     <t>AICE CHOCO MALLOW350</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>20141097</t>
   </si>
   <si>
     <t>AICE COOKS.CHUNKY350</t>
-  </si>
-  <si>
-    <t>16</t>
   </si>
 </sst>
 </file>
@@ -583,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -805,10 +817,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
@@ -816,30 +828,30 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -848,18 +860,18 @@
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -868,18 +880,18 @@
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -888,18 +900,18 @@
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -908,7 +920,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>13</v>
@@ -916,10 +928,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -928,7 +940,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>13</v>
@@ -936,10 +948,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -948,7 +960,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>13</v>
@@ -956,10 +968,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -968,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>13</v>
@@ -976,10 +988,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -988,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>13</v>
@@ -996,10 +1008,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1008,7 +1020,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>13</v>
@@ -1016,10 +1028,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1028,9 +1040,49 @@
         <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>13</v>
       </c>
     </row>
